--- a/src/main/resources/Company_Names.xlsx
+++ b/src/main/resources/Company_Names.xlsx
@@ -1223,7 +1223,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="C2">
         <v>1.45</v>
@@ -1234,7 +1234,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>1975.75</v>
+        <v>1991.45</v>
       </c>
       <c r="C3" s="1">
         <v>1351.65</v>
